--- a/docs/planilha-atributos-carreta-dre.xlsx
+++ b/docs/planilha-atributos-carreta-dre.xlsx
@@ -2353,7 +2353,7 @@
   <autoFilter ref="A1:E65"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D65" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Categoria DRE - Sintético" error="Use um dos seis sintéticos da aba Categorias DRE." type="list">
-      <formula1>"Receita bruta,(−) Deduções,(−) Custo variável,(−) Custo fixo,(−) Depreciação e financeiro,Não entra na DRE"</formula1>
+      <formula1>"Receita bruta,(−) Deduções,(−) Custo variável,(−) Custo fixo,(−) Depreciação e financeiro,Subtotal e margem,Não entra na DRE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
